--- a/healthcare_forms/022_sleep_disorder_diagnosis_form--healthcare_forms.xlsx
+++ b/healthcare_forms/022_sleep_disorder_diagnosis_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>very_much</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>Very much</t>
         </is>
       </c>
     </row>
@@ -1019,29 +1019,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>very_much</t>
+          <t>extremely_much</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Very much</t>
+          <t>Extremely much</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sleepiness_choices</t>
+          <t>snore_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>extremely_much</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Extremely much</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1053,29 +1053,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>snore_choices</t>
+          <t>medication_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1138,29 +1138,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>at_night</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>At night</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>medication_choices</t>
+          <t>medical_conditions_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>at_night</t>
+          <t>insomnia</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>At night</t>
+          <t>Insomnia</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>insomnia</t>
+          <t>sleep_disorder</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>Sleep disorder</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sleep_disorder</t>
+          <t>narcolepsy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sleep disorder</t>
+          <t>Narcolepsy</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>narcolepsy</t>
+          <t>sleep_apnea</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Narcolepsy</t>
+          <t>Sleep apnea</t>
         </is>
       </c>
     </row>
@@ -1223,29 +1223,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sleep_apnea</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sleep apnea</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_treatments_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1257,27 +1257,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>medical_treatments_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>None</t>
         </is>
